--- a/Shared/Configs/Datas/gameplay/role.xlsx
+++ b/Shared/Configs/Datas/gameplay/role.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\WECS-BATTLE\Shared\Configs\Datas\gameplay\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\WECS\Shared\Configs\Datas\gameplay\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB41DE4-B5E1-4CD9-AD0C-C39309C61222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -29,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="288">
   <si>
     <t>##var</t>
   </si>
@@ -223,9 +222,6 @@
     <t>idle</t>
   </si>
   <si>
-    <t>move</t>
-  </si>
-  <si>
     <t>damage</t>
   </si>
   <si>
@@ -253,9 +249,6 @@
     <t>待机</t>
   </si>
   <si>
-    <t>移动</t>
-  </si>
-  <si>
     <t>受伤</t>
   </si>
   <si>
@@ -893,19 +886,33 @@
   </si>
   <si>
     <t>Passive_&lt;Class&gt;_&lt;Name&gt;，如 Passive_Knight_Indomitable</t>
+  </si>
+  <si>
+    <t>walk</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>走动</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>run</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>跑动</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk_F</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -936,7 +943,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -948,153 +955,45 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11.25"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1131,188 +1030,8 @@
         <bgColor rgb="FFE0FFF4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1365,256 +1084,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1630,7 +1110,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1657,62 +1137,25 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1962,27 +1405,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.9090909090909" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5454545454545" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.54545454545454" style="1" customWidth="1"/>
-    <col min="7" max="11" width="5.54545454545455" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="1" customWidth="1"/>
+    <col min="7" max="11" width="5.5" style="1" customWidth="1"/>
     <col min="12" max="13" width="8" style="1" customWidth="1"/>
     <col min="16" max="16" width="8" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2033,7 +1476,7 @@
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" customFormat="1" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
@@ -2084,7 +1527,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" s="7" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="3" spans="1:25" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2124,7 +1567,7 @@
       <c r="M3" s="11"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="4" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -2164,7 +1607,7 @@
       <c r="M4" s="12"/>
       <c r="P4" s="12"/>
     </row>
-    <row r="5" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="5" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -2204,7 +1647,7 @@
       <c r="M5" s="12"/>
       <c r="P5" s="12"/>
     </row>
-    <row r="6" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="6" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2244,7 +1687,7 @@
       <c r="M6" s="12"/>
       <c r="P6" s="12"/>
     </row>
-    <row r="7" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="7" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -2284,7 +1727,7 @@
       <c r="M7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="8" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2324,7 +1767,7 @@
       <c r="M8" s="12"/>
       <c r="P8" s="12"/>
     </row>
-    <row r="9" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="9" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -2364,7 +1807,7 @@
       <c r="M9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="10" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2404,7 +1847,7 @@
       <c r="M10" s="12"/>
       <c r="P10" s="12"/>
     </row>
-    <row r="11" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="11" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2444,7 +1887,7 @@
       <c r="M11" s="12"/>
       <c r="P11" s="12"/>
     </row>
-    <row r="12" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="12" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2484,7 +1927,7 @@
       <c r="M12" s="12"/>
       <c r="P12" s="12"/>
     </row>
-    <row r="13" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="13" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -2524,7 +1967,7 @@
       <c r="M13" s="12"/>
       <c r="P13" s="12"/>
     </row>
-    <row r="14" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="14" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2564,7 +2007,7 @@
       <c r="M14" s="12"/>
       <c r="P14" s="12"/>
     </row>
-    <row r="15" s="8" customFormat="1" ht="17" customHeight="1" spans="1:25">
+    <row r="15" spans="1:25" s="8" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2604,42 +2047,41 @@
       <c r="M15" s="12"/>
       <c r="P15" s="12"/>
     </row>
-    <row r="16" s="1" customFormat="1"/>
-    <row r="17" s="1" customFormat="1"/>
-    <row r="18" s="1" customFormat="1"/>
-    <row r="19" s="1" customFormat="1"/>
-    <row r="20" s="1" customFormat="1"/>
-    <row r="21" s="1" customFormat="1"/>
-    <row r="22" s="1" customFormat="1"/>
-    <row r="23" s="1" customFormat="1"/>
-    <row r="24" s="1" customFormat="1"/>
-    <row r="25" s="1" customFormat="1"/>
-    <row r="26" s="1" customFormat="1"/>
-    <row r="27" s="1" customFormat="1"/>
-    <row r="28" s="1" customFormat="1"/>
-    <row r="29" s="1" customFormat="1"/>
-    <row r="30" s="1" customFormat="1"/>
+    <row r="16" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="19" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="20" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="21" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="22" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="23" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="24" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="25" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="26" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="27" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="28" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="29" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="15.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="10.6363636363636" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.54545454545455" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.6363636363636" style="2" customWidth="1"/>
-    <col min="11" max="12" width="9.54545454545454" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="2" customWidth="1"/>
+    <col min="12" max="13" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:18">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2655,35 +2097,38 @@
       <c r="E1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
-    </row>
-    <row r="2" customFormat="1" spans="1:18">
+      <c r="S1" s="6"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -2691,78 +2136,84 @@
         <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="K2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="S2" s="6"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B3" s="1">
         <v>10001</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
         <v>77</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="G3" t="s">
         <v>78</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>79</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>80</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>81</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>82</v>
       </c>
-      <c r="I3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" t="s">
         <v>66</v>
       </c>
-      <c r="L3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:18">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B4" s="1">
         <v>103261</v>
       </c>
@@ -2770,44 +2221,44 @@
         <v>103261</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" t="s">
         <v>85</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>86</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>87</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>88</v>
       </c>
-      <c r="I4" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" t="s">
         <v>66</v>
       </c>
-      <c r="L4" t="s">
-        <v>67</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
@@ -2819,355 +2270,354 @@
     <col min="8" max="8" width="18" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:8">
+    <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="2" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="3" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="4" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="5" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="6" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:8">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="G7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="8" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="G8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="9" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:8">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="11" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="G11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="12" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="G12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:8">
+    </row>
+    <row r="13" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="G13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>148</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="2" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" customWidth="1"/>
@@ -3177,78 +2627,78 @@
     <col min="7" max="7" width="60" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:7">
+    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="3" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" s="4">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="4" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>31</v>
@@ -3257,21 +2707,21 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="5" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>31</v>
@@ -3280,21 +2730,21 @@
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="6" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>34</v>
@@ -3303,21 +2753,21 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="7" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>34</v>
@@ -3326,21 +2776,21 @@
         <v>2</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="8" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>37</v>
@@ -3349,21 +2799,21 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="9" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>37</v>
@@ -3372,21 +2822,21 @@
         <v>2</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="10" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>40</v>
@@ -3395,21 +2845,21 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="11" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>40</v>
@@ -3418,21 +2868,21 @@
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="12" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>43</v>
@@ -3441,21 +2891,21 @@
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="13" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>43</v>
@@ -3464,21 +2914,21 @@
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="14" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>46</v>
@@ -3487,21 +2937,21 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="15" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>46</v>
@@ -3510,21 +2960,21 @@
         <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="16" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>48</v>
@@ -3533,21 +2983,21 @@
         <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="17" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>48</v>
@@ -3556,21 +3006,21 @@
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="18" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>50</v>
@@ -3579,21 +3029,21 @@
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="19" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>50</v>
@@ -3602,21 +3052,21 @@
         <v>2</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="20" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>52</v>
@@ -3625,21 +3075,21 @@
         <v>1</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="21" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>52</v>
@@ -3648,21 +3098,21 @@
         <v>2</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="22" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>54</v>
@@ -3671,21 +3121,21 @@
         <v>1</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="23" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>54</v>
@@ -3694,21 +3144,21 @@
         <v>2</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="24" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>56</v>
@@ -3717,21 +3167,21 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:7">
+    </row>
+    <row r="25" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>56</v>
@@ -3740,29 +3190,28 @@
         <v>2</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>228</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="2" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" customWidth="1"/>
@@ -3771,334 +3220,332 @@
     <col min="5" max="5" width="53" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="3" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="4" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="6" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="7" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="8" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="9" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="10" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="11" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="12" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:5">
+    </row>
+    <row r="13" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>266</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20" style="2" customWidth="1"/>
     <col min="2" max="2" width="60" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:2">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:2">
-      <c r="A2" s="4" t="s">
+    <row r="3" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:2">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:2">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:2">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:2">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:2">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="1:2">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="1:2">
-      <c r="A9" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="B1:E1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="8.72727272727273" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54545454545454" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.09090909090909" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.54545454545454" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="2" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Shared/Configs/Datas/gameplay/role.xlsx
+++ b/Shared/Configs/Datas/gameplay/role.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\WECS\Shared\Configs\Datas\gameplay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB41DE4-B5E1-4CD9-AD0C-C39309C61222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824F2999-0E89-4DEC-8BA8-DD2F83FDF13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="3990" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="290">
   <si>
     <t>##var</t>
   </si>
@@ -905,6 +905,14 @@
   </si>
   <si>
     <t>Walk_F</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>animation</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2071,17 +2079,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="2" customWidth="1"/>
-    <col min="12" max="13" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="2" customWidth="1"/>
+    <col min="13" max="14" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2091,44 +2100,47 @@
       <c r="C1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
       <c r="S1" s="6"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="T1" s="6"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -2138,113 +2150,122 @@
       <c r="C2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="T2" s="6"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="B3" s="1">
         <v>10001</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E3" t="s">
         <v>76</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>78</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>79</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>80</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>81</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>82</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>65</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.15">
       <c r="B4" s="1">
         <v>103261</v>
       </c>
       <c r="C4" s="1">
         <v>103261</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1">
+        <v>103261</v>
+      </c>
+      <c r="E4" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>83</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>84</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>85</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>86</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>87</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>88</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>65</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>66</v>
       </c>
     </row>
